--- a/data/annual_loads_stations.xlsx
+++ b/data/annual_loads_stations.xlsx
@@ -4243,7 +4243,7 @@
         <v>0.670718985936172</v>
       </c>
       <c r="E177" t="n">
-        <v>298.005702836161</v>
+        <v>216.0726392431546</v>
       </c>
       <c r="F177" t="n">
         <v>195.8554627484408</v>
@@ -6103,13 +6103,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.3864762307712328</v>
+        <v>0.5361867719001741</v>
       </c>
       <c r="H36" t="n">
-        <v>27.97194516858735</v>
+        <v>14.34707384285408</v>
       </c>
       <c r="I36" t="n">
-        <v>125.0628069142367</v>
+        <v>87.55136360349167</v>
       </c>
       <c r="J36" t="n">
         <v>-79.39285653432115</v>

--- a/data/annual_loads_stations.xlsx
+++ b/data/annual_loads_stations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F190"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,2998 +1516,3748 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1995</v>
+        <v>1981</v>
       </c>
       <c r="C51" t="n">
-        <v>216.5177960450953</v>
+        <v>341.5718911809507</v>
       </c>
       <c r="D51" t="n">
-        <v>6.619594004249908</v>
+        <v>68.88070017698745</v>
       </c>
       <c r="E51" t="n">
-        <v>3180.144565744456</v>
-      </c>
-      <c r="F51" t="n">
-        <v>948.6323535620309</v>
-      </c>
+        <v>69722.74905802809</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1996</v>
+        <v>1982</v>
       </c>
       <c r="C52" t="n">
-        <v>205.1468362375021</v>
+        <v>350.9306177698232</v>
       </c>
       <c r="D52" t="n">
-        <v>6.883637384149339</v>
+        <v>61.08454337473096</v>
       </c>
       <c r="E52" t="n">
-        <v>2962.508476689706</v>
-      </c>
-      <c r="F52" t="n">
-        <v>676.6893552491267</v>
-      </c>
+        <v>61806.73815214165</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1997</v>
+        <v>1983</v>
       </c>
       <c r="C53" t="n">
-        <v>196.3361179247576</v>
+        <v>657.0929865813411</v>
       </c>
       <c r="D53" t="n">
-        <v>5.923668309121244</v>
+        <v>109.0829169864744</v>
       </c>
       <c r="E53" t="n">
-        <v>2828.564435593198</v>
+        <v>73242.07999233792</v>
       </c>
       <c r="F53" t="n">
-        <v>707.6172625228901</v>
+        <v>3408.317660432497</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1998</v>
+        <v>1984</v>
       </c>
       <c r="C54" t="n">
-        <v>226.3609882392294</v>
+        <v>319.0059084347085</v>
       </c>
       <c r="D54" t="n">
-        <v>12.19346521545144</v>
+        <v>59.74434396034099</v>
       </c>
       <c r="E54" t="n">
-        <v>5199.694952696468</v>
+        <v>39725.28535748641</v>
       </c>
       <c r="F54" t="n">
-        <v>1007.593700058762</v>
+        <v>1515.78967434071</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1999</v>
+        <v>1985</v>
       </c>
       <c r="C55" t="n">
-        <v>230.9544232569506</v>
+        <v>450.7564596049893</v>
       </c>
       <c r="D55" t="n">
-        <v>8.210959291674046</v>
+        <v>91.13844874216676</v>
       </c>
       <c r="E55" t="n">
-        <v>3136.114786557891</v>
+        <v>67228.40194676658</v>
       </c>
       <c r="F55" t="n">
-        <v>1219.598775148054</v>
+        <v>2762.944957636344</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2000</v>
+        <v>1986</v>
       </c>
       <c r="C56" t="n">
-        <v>341.1327594780858</v>
+        <v>401.1315191659745</v>
       </c>
       <c r="D56" t="n">
-        <v>20.8977541489777</v>
+        <v>112.6721601297674</v>
       </c>
       <c r="E56" t="n">
-        <v>10439.39329644675</v>
+        <v>85043.54759923773</v>
       </c>
       <c r="F56" t="n">
-        <v>2126.151506620473</v>
+        <v>1838.949195737632</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2001</v>
+        <v>1987</v>
       </c>
       <c r="C57" t="n">
-        <v>232.6599736977205</v>
+        <v>550.1308471074173</v>
       </c>
       <c r="D57" t="n">
-        <v>8.531292542914452</v>
+        <v>80.53217112657494</v>
       </c>
       <c r="E57" t="n">
-        <v>4022.798954165779</v>
+        <v>62979.62766458619</v>
       </c>
       <c r="F57" t="n">
-        <v>977.1692635698893</v>
+        <v>2679.082903614887</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2002</v>
+        <v>1988</v>
       </c>
       <c r="C58" t="n">
-        <v>193.4823008660429</v>
+        <v>592.0397129401465</v>
       </c>
       <c r="D58" t="n">
-        <v>5.980029879293789</v>
+        <v>124.7049929715174</v>
       </c>
       <c r="E58" t="n">
-        <v>1542.14664284893</v>
+        <v>105192.292985107</v>
       </c>
       <c r="F58" t="n">
-        <v>803.9526811440414</v>
+        <v>2944.552674263607</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2003</v>
+        <v>1989</v>
       </c>
       <c r="C59" t="n">
-        <v>230.8792691072831</v>
+        <v>468.4701120422085</v>
       </c>
       <c r="D59" t="n">
-        <v>3.738066666042583</v>
+        <v>49.2638581231333</v>
       </c>
       <c r="E59" t="n">
-        <v>1166.433842189165</v>
+        <v>44357.00247555786</v>
       </c>
       <c r="F59" t="n">
-        <v>824.7500032227753</v>
+        <v>1510.578134983172</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2004</v>
+        <v>1990</v>
       </c>
       <c r="C60" t="n">
-        <v>284.5640308139873</v>
+        <v>349.4746974171982</v>
       </c>
       <c r="D60" t="n">
-        <v>6.784000855710963</v>
+        <v>73.73095445500346</v>
       </c>
       <c r="E60" t="n">
-        <v>1482.588642788291</v>
+        <v>75378.11162331865</v>
       </c>
       <c r="F60" t="n">
-        <v>985.3322592379582</v>
+        <v>1324.257597784072</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2005</v>
+        <v>1991</v>
       </c>
       <c r="C61" t="n">
-        <v>262.2600052922739</v>
+        <v>391.7494949270902</v>
       </c>
       <c r="D61" t="n">
-        <v>5.765697037074019</v>
+        <v>37.58592499131225</v>
       </c>
       <c r="E61" t="n">
-        <v>1914.754032647017</v>
+        <v>36958.80319249671</v>
       </c>
       <c r="F61" t="n">
-        <v>811.1675350918348</v>
+        <v>1557.180607497606</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2006</v>
+        <v>1992</v>
       </c>
       <c r="C62" t="n">
-        <v>260.5301833090566</v>
+        <v>414.9108892957654</v>
       </c>
       <c r="D62" t="n">
-        <v>8.378471452309405</v>
+        <v>56.10635386472894</v>
       </c>
       <c r="E62" t="n">
-        <v>2736.879223050535</v>
+        <v>49529.31014653804</v>
       </c>
       <c r="F62" t="n">
-        <v>1243.283273626793</v>
+        <v>1364.626829473634</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2008</v>
+        <v>1993</v>
       </c>
       <c r="C63" t="n">
-        <v>266.4378611183134</v>
+        <v>590.4658793051839</v>
       </c>
       <c r="D63" t="n">
-        <v>13.12391077468133</v>
+        <v>43.87309314577687</v>
       </c>
       <c r="E63" t="n">
-        <v>3910.79094850505</v>
+        <v>37260.79901700516</v>
       </c>
       <c r="F63" t="n">
-        <v>1350.351452849043</v>
+        <v>3025.677748332746</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2010</v>
+        <v>1994</v>
       </c>
       <c r="C64" t="n">
-        <v>188.740936951179</v>
+        <v>519.7065631029467</v>
       </c>
       <c r="D64" t="n">
-        <v>4.810128547269732</v>
+        <v>43.0445486911438</v>
       </c>
       <c r="E64" t="n">
-        <v>2043.760149084331</v>
+        <v>36211.50651253057</v>
       </c>
       <c r="F64" t="n">
-        <v>826.5717141899352</v>
+        <v>2142.217653411211</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2011</v>
+        <v>1995</v>
       </c>
       <c r="C65" t="n">
-        <v>256.7366468616509</v>
+        <v>471.2158459945406</v>
       </c>
       <c r="D65" t="n">
-        <v>18.54963244292455</v>
+        <v>40.86670498081531</v>
       </c>
       <c r="E65" t="n">
-        <v>10528.90858339543</v>
+        <v>34806.91346634379</v>
       </c>
       <c r="F65" t="n">
-        <v>1482.354586999677</v>
+        <v>2006.827042761013</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2012</v>
+        <v>1997</v>
       </c>
       <c r="C66" t="n">
-        <v>280.7240502987199</v>
+        <v>378.3751703962691</v>
       </c>
       <c r="D66" t="n">
-        <v>9.817256696488759</v>
+        <v>27.73582692545794</v>
       </c>
       <c r="E66" t="n">
-        <v>5320.726892220153</v>
+        <v>21704.97112317758</v>
       </c>
       <c r="F66" t="n">
-        <v>1337.501895882453</v>
+        <v>1450.040306582756</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2013</v>
+        <v>1998</v>
       </c>
       <c r="C67" t="n">
-        <v>279.5106688300704</v>
+        <v>392.7437582776994</v>
       </c>
       <c r="D67" t="n">
-        <v>19.61633942118484</v>
+        <v>19.04700008403122</v>
       </c>
       <c r="E67" t="n">
-        <v>14273.98569047706</v>
+        <v>7893.948775182404</v>
       </c>
       <c r="F67" t="n">
-        <v>1369.144592361439</v>
+        <v>1899.949234040725</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2015</v>
+        <v>1999</v>
       </c>
       <c r="C68" t="n">
-        <v>281.391781661804</v>
+        <v>499.7162384669145</v>
       </c>
       <c r="D68" t="n">
-        <v>6.919611375126133</v>
+        <v>82.0539948114979</v>
       </c>
       <c r="E68" t="n">
-        <v>3160.05044952898</v>
+        <v>73983.0819251833</v>
       </c>
       <c r="F68" t="n">
-        <v>1814.596068371525</v>
+        <v>2669.799174037153</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2016</v>
+        <v>2000</v>
       </c>
       <c r="C69" t="n">
-        <v>193.5739349988294</v>
+        <v>664.0990720840666</v>
       </c>
       <c r="D69" t="n">
-        <v>4.615766964464658</v>
+        <v>162.476260338829</v>
       </c>
       <c r="E69" t="n">
-        <v>2117.966123631714</v>
+        <v>148985.2105753848</v>
       </c>
       <c r="F69" t="n">
-        <v>1169.255413566833</v>
+        <v>4248.40427135238</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="C70" t="n">
-        <v>258.0705993943514</v>
+        <v>386.3135475376498</v>
       </c>
       <c r="D70" t="n">
-        <v>6.676136012961517</v>
+        <v>54.44317756836011</v>
       </c>
       <c r="E70" t="n">
-        <v>2556.496479314575</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
+        <v>49289.40801410704</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2022.539862728412</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2018</v>
+        <v>2002</v>
       </c>
       <c r="C71" t="n">
-        <v>311.7907018047362</v>
+        <v>361.3321360796039</v>
       </c>
       <c r="D71" t="n">
-        <v>11.58756978807228</v>
+        <v>40.67594787687414</v>
       </c>
       <c r="E71" t="n">
-        <v>6344.764701752276</v>
-      </c>
-      <c r="F71" t="inlineStr"/>
+        <v>36424.11797397079</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1438.885756059304</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2020</v>
+        <v>2003</v>
       </c>
       <c r="C72" t="n">
-        <v>346.7191883603683</v>
+        <v>520.2284056513188</v>
       </c>
       <c r="D72" t="n">
-        <v>23.03373067151695</v>
+        <v>42.87283956186766</v>
       </c>
       <c r="E72" t="n">
-        <v>10242.86875527961</v>
+        <v>37672.2892774871</v>
       </c>
       <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2023</v>
+        <v>2004</v>
       </c>
       <c r="C73" t="n">
-        <v>313.2001009260769</v>
+        <v>443.852626398274</v>
       </c>
       <c r="D73" t="n">
-        <v>8.551356125382863</v>
+        <v>28.78211428095639</v>
       </c>
       <c r="E73" t="n">
-        <v>1803.274423131739</v>
-      </c>
-      <c r="F73" t="n">
-        <v>2844.543528890281</v>
-      </c>
+        <v>21749.02673135707</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2024</v>
+        <v>2005</v>
       </c>
       <c r="C74" t="n">
-        <v>309.2023526492062</v>
+        <v>300.3739810651741</v>
       </c>
       <c r="D74" t="n">
-        <v>8.112949745931397</v>
+        <v>17.94877451716364</v>
       </c>
       <c r="E74" t="n">
-        <v>4538.9274088344</v>
-      </c>
-      <c r="F74" t="n">
-        <v>2692.086141824332</v>
-      </c>
+        <v>12572.39435103489</v>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1998</v>
+        <v>2006</v>
       </c>
       <c r="C75" t="n">
-        <v>511.7779201959133</v>
+        <v>742.6825591120353</v>
       </c>
       <c r="D75" t="n">
-        <v>36.19501564136775</v>
+        <v>77.40336108682922</v>
       </c>
       <c r="E75" t="n">
-        <v>31282.05596369573</v>
-      </c>
-      <c r="F75" t="n">
-        <v>2324.342543692302</v>
-      </c>
+        <v>58418.63569389972</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="C76" t="n">
-        <v>472.7224528559897</v>
+        <v>346.1515356812237</v>
       </c>
       <c r="D76" t="n">
-        <v>48.50897211804379</v>
-      </c>
-      <c r="E76" t="n">
-        <v>42066.63358051859</v>
-      </c>
-      <c r="F76" t="n">
-        <v>2991.150563315237</v>
-      </c>
+        <v>32.82774293799634</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="C77" t="n">
-        <v>658.0717263768403</v>
+        <v>543.3230000610744</v>
       </c>
       <c r="D77" t="n">
-        <v>149.0405328869568</v>
-      </c>
-      <c r="E77" t="n">
-        <v>125467.5183689415</v>
-      </c>
+        <v>62.68530889737348</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="C78" t="n">
-        <v>331.4877721201903</v>
+        <v>956.0796890057065</v>
       </c>
       <c r="D78" t="n">
-        <v>50.18979259735507</v>
+        <v>132.0760478158835</v>
       </c>
       <c r="E78" t="n">
-        <v>44575.50652778852</v>
-      </c>
-      <c r="F78" t="inlineStr"/>
+        <v>121038.9825242647</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2581.552582598923</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="C79" t="n">
-        <v>294.5415371642576</v>
+        <v>511.7962299387671</v>
       </c>
       <c r="D79" t="n">
-        <v>29.14598483225638</v>
+        <v>41.4334908143132</v>
       </c>
       <c r="E79" t="n">
-        <v>26665.21677702123</v>
-      </c>
-      <c r="F79" t="inlineStr"/>
+        <v>34343.01240844018</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2485.224235803863</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="C80" t="n">
-        <v>506.2812781192748</v>
+        <v>489.8346987901155</v>
       </c>
       <c r="D80" t="n">
-        <v>37.49690548117942</v>
+        <v>78.47472314547689</v>
       </c>
       <c r="E80" t="n">
-        <v>34221.37857013181</v>
-      </c>
-      <c r="F80" t="inlineStr"/>
+        <v>74141.12267447691</v>
+      </c>
+      <c r="F80" t="n">
+        <v>3193.091464741668</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="C81" t="n">
-        <v>316.7817410885504</v>
+        <v>499.19435039555</v>
       </c>
       <c r="D81" t="n">
-        <v>25.30924364201172</v>
+        <v>67.53485743378863</v>
       </c>
       <c r="E81" t="n">
-        <v>18704.70590562527</v>
-      </c>
-      <c r="F81" t="inlineStr"/>
+        <v>67086.73320058618</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3792.494425414417</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2006</v>
+        <v>2015</v>
       </c>
       <c r="C82" t="n">
-        <v>742.5659804690229</v>
+        <v>422.9344024247412</v>
       </c>
       <c r="D82" t="n">
-        <v>38.98089422772803</v>
+        <v>32.06763920245741</v>
       </c>
       <c r="E82" t="n">
-        <v>38253.94476862722</v>
-      </c>
-      <c r="F82" t="inlineStr"/>
+        <v>27949.31308569487</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3078.342099500841</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1980</v>
+        <v>2016</v>
       </c>
       <c r="C83" t="n">
-        <v>505.5180966059012</v>
+        <v>458.9540965061149</v>
       </c>
       <c r="D83" t="n">
-        <v>21.15775274858974</v>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+        <v>95.1274940376647</v>
+      </c>
+      <c r="E83" t="n">
+        <v>107558.7203164238</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2594.788430374835</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1981</v>
+        <v>2020</v>
       </c>
       <c r="C84" t="n">
-        <v>550.3758486272691</v>
+        <v>583.092847400176</v>
       </c>
       <c r="D84" t="n">
-        <v>34.93460434676286</v>
+        <v>36.67633145216725</v>
       </c>
       <c r="E84" t="n">
-        <v>5632.526421804672</v>
+        <v>22613.13954840291</v>
       </c>
       <c r="F84" t="n">
-        <v>1222.747684883211</v>
+        <v>4170.765550549238</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1982</v>
+        <v>2023</v>
       </c>
       <c r="C85" t="n">
-        <v>370.5516062726167</v>
+        <v>517.7946404231568</v>
       </c>
       <c r="D85" t="n">
-        <v>23.32581395234075</v>
+        <v>40.35893147051913</v>
       </c>
       <c r="E85" t="n">
-        <v>4967.043752943522</v>
+        <v>30961.97470490552</v>
       </c>
       <c r="F85" t="n">
-        <v>1468.730551916253</v>
+        <v>5180.728355158541</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1983</v>
+        <v>1995</v>
       </c>
       <c r="C86" t="n">
-        <v>649.8509995284052</v>
+        <v>216.5177960450953</v>
       </c>
       <c r="D86" t="n">
-        <v>40.53987019922116</v>
+        <v>6.619594004249908</v>
       </c>
       <c r="E86" t="n">
-        <v>15526.71588886437</v>
-      </c>
-      <c r="F86" t="inlineStr"/>
+        <v>3180.144565744456</v>
+      </c>
+      <c r="F86" t="n">
+        <v>948.6323535620309</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1987</v>
+        <v>1996</v>
       </c>
       <c r="C87" t="n">
-        <v>676.6764336526682</v>
+        <v>205.1468362375021</v>
       </c>
       <c r="D87" t="n">
-        <v>86.82209565769185</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>6.883637384149339</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2962.508476689706</v>
+      </c>
       <c r="F87" t="n">
-        <v>2100.242447930635</v>
+        <v>676.6893552491267</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1988</v>
+        <v>1997</v>
       </c>
       <c r="C88" t="n">
-        <v>406.8379156336074</v>
+        <v>196.3361179247576</v>
       </c>
       <c r="D88" t="n">
-        <v>6.463634185600521</v>
+        <v>5.923668309121244</v>
       </c>
       <c r="E88" t="n">
-        <v>5394.759924488313</v>
+        <v>2828.564435593198</v>
       </c>
       <c r="F88" t="n">
-        <v>1956.35041097056</v>
+        <v>707.6172625228901</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1989</v>
+        <v>1998</v>
       </c>
       <c r="C89" t="n">
-        <v>511.3170949557855</v>
+        <v>226.3609882392294</v>
       </c>
       <c r="D89" t="n">
-        <v>12.63927178839586</v>
+        <v>12.19346521545144</v>
       </c>
       <c r="E89" t="n">
-        <v>4460.441339471327</v>
+        <v>5199.694952696468</v>
       </c>
       <c r="F89" t="n">
-        <v>1044.896885386453</v>
+        <v>1007.593700058762</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1990</v>
+        <v>1999</v>
       </c>
       <c r="C90" t="n">
-        <v>649.9202417294422</v>
+        <v>230.9544232569506</v>
       </c>
       <c r="D90" t="n">
-        <v>17.57738690046505</v>
+        <v>8.210959291674046</v>
       </c>
       <c r="E90" t="n">
-        <v>8214.948755565014</v>
+        <v>3136.114786557891</v>
       </c>
       <c r="F90" t="n">
-        <v>979.7220276811303</v>
+        <v>1219.598775148054</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1991</v>
+        <v>2000</v>
       </c>
       <c r="C91" t="n">
-        <v>778.7265232398832</v>
+        <v>341.1327594780858</v>
       </c>
       <c r="D91" t="n">
-        <v>10.38404257891497</v>
+        <v>20.8977541489777</v>
       </c>
       <c r="E91" t="n">
-        <v>4591.88857371901</v>
-      </c>
-      <c r="F91" t="inlineStr"/>
+        <v>10439.39329644675</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2126.151506620473</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1992</v>
+        <v>2001</v>
       </c>
       <c r="C92" t="n">
-        <v>370.8779181844769</v>
+        <v>232.6599736977205</v>
       </c>
       <c r="D92" t="n">
-        <v>6.347507473798679</v>
+        <v>8.531292542914452</v>
       </c>
       <c r="E92" t="n">
-        <v>2493.370999714289</v>
+        <v>4022.798954165779</v>
       </c>
       <c r="F92" t="n">
-        <v>938.677394480183</v>
+        <v>977.1692635698893</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1993</v>
+        <v>2002</v>
       </c>
       <c r="C93" t="n">
-        <v>472.877631237185</v>
+        <v>193.4823008660429</v>
       </c>
       <c r="D93" t="n">
-        <v>11.59048939228629</v>
+        <v>5.980029879293789</v>
       </c>
       <c r="E93" t="n">
-        <v>4019.524580910777</v>
+        <v>1542.14664284893</v>
       </c>
       <c r="F93" t="n">
-        <v>1367.368373150696</v>
+        <v>803.9526811440414</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1994</v>
+        <v>2003</v>
       </c>
       <c r="C94" t="n">
-        <v>1085.256507357366</v>
+        <v>230.8792691072831</v>
       </c>
       <c r="D94" t="n">
-        <v>17.94727561707502</v>
+        <v>3.738066666042583</v>
       </c>
       <c r="E94" t="n">
-        <v>2806.311770386166</v>
+        <v>1166.433842189165</v>
       </c>
       <c r="F94" t="n">
-        <v>2028.655443525404</v>
+        <v>824.7500032227753</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1995</v>
+        <v>2004</v>
       </c>
       <c r="C95" t="n">
-        <v>509.7551644368058</v>
+        <v>284.5640308139873</v>
       </c>
       <c r="D95" t="n">
-        <v>9.576232613433445</v>
+        <v>6.784000855710963</v>
       </c>
       <c r="E95" t="n">
-        <v>3225.053974292888</v>
+        <v>1482.588642788291</v>
       </c>
       <c r="F95" t="n">
-        <v>1232.042043959136</v>
+        <v>985.3322592379582</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1996</v>
+        <v>2005</v>
       </c>
       <c r="C96" t="n">
-        <v>499.3596956523585</v>
+        <v>262.2600052922739</v>
       </c>
       <c r="D96" t="n">
-        <v>6.996084150222485</v>
+        <v>5.765697037074019</v>
       </c>
       <c r="E96" t="n">
-        <v>2300.830588629901</v>
+        <v>1914.754032647017</v>
       </c>
       <c r="F96" t="n">
-        <v>815.4925754911436</v>
+        <v>811.1675350918348</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1997</v>
+        <v>2006</v>
       </c>
       <c r="C97" t="n">
-        <v>719.8730708974265</v>
+        <v>260.5301833090566</v>
       </c>
       <c r="D97" t="n">
-        <v>12.93259490101161</v>
+        <v>8.378471452309405</v>
       </c>
       <c r="E97" t="n">
-        <v>4200.335831863231</v>
+        <v>2736.879223050535</v>
       </c>
       <c r="F97" t="n">
-        <v>1022.443871051485</v>
+        <v>1243.283273626793</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="C98" t="n">
-        <v>638.6742833177299</v>
+        <v>266.4378611183134</v>
       </c>
       <c r="D98" t="n">
-        <v>17.79439531362919</v>
+        <v>13.12391077468133</v>
       </c>
       <c r="E98" t="n">
-        <v>6204.300176263578</v>
+        <v>3910.79094850505</v>
       </c>
       <c r="F98" t="n">
-        <v>1320.302739733719</v>
+        <v>1350.351452849043</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="C99" t="n">
-        <v>623.1556853516021</v>
+        <v>188.740936951179</v>
       </c>
       <c r="D99" t="n">
-        <v>16.90767448409418</v>
+        <v>4.810128547269732</v>
       </c>
       <c r="E99" t="n">
-        <v>7079.726346128299</v>
+        <v>2043.760149084331</v>
       </c>
       <c r="F99" t="n">
-        <v>2127.784367944353</v>
+        <v>826.5717141899352</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2000</v>
+        <v>2011</v>
       </c>
       <c r="C100" t="n">
-        <v>820.6835736131554</v>
+        <v>256.7366468616509</v>
       </c>
       <c r="D100" t="n">
-        <v>37.23347712024713</v>
+        <v>18.54963244292455</v>
       </c>
       <c r="E100" t="n">
-        <v>17073.01088071766</v>
+        <v>10528.90858339543</v>
       </c>
       <c r="F100" t="n">
-        <v>3114.422018139068</v>
+        <v>1482.354586999677</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2001</v>
+        <v>2012</v>
       </c>
       <c r="C101" t="n">
-        <v>664.6564457996925</v>
+        <v>280.7240502987199</v>
       </c>
       <c r="D101" t="n">
-        <v>25.53768851400098</v>
+        <v>9.817256696488759</v>
       </c>
       <c r="E101" t="n">
-        <v>18626.20105913134</v>
+        <v>5320.726892220153</v>
       </c>
       <c r="F101" t="n">
-        <v>1772.998760300929</v>
+        <v>1337.501895882453</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="C102" t="n">
-        <v>857.7224085594355</v>
+        <v>279.5106688300704</v>
       </c>
       <c r="D102" t="n">
-        <v>10.34244300971466</v>
+        <v>19.61633942118484</v>
       </c>
       <c r="E102" t="n">
-        <v>2632.664145744585</v>
+        <v>14273.98569047706</v>
       </c>
       <c r="F102" t="n">
-        <v>1509.466717849222</v>
+        <v>1369.144592361439</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2003</v>
+        <v>2015</v>
       </c>
       <c r="C103" t="n">
-        <v>731.5229103605973</v>
+        <v>281.391781661804</v>
       </c>
       <c r="D103" t="n">
-        <v>5.254392900864078</v>
+        <v>6.919611375126133</v>
       </c>
       <c r="E103" t="n">
-        <v>1937.873751400207</v>
+        <v>3160.05044952898</v>
       </c>
       <c r="F103" t="n">
-        <v>1091.024638202054</v>
+        <v>1814.596068371525</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2004</v>
+        <v>2016</v>
       </c>
       <c r="C104" t="n">
-        <v>482.8510458880432</v>
+        <v>193.5739349988294</v>
       </c>
       <c r="D104" t="n">
-        <v>9.483917002062677</v>
+        <v>4.615766964464658</v>
       </c>
       <c r="E104" t="n">
-        <v>1932.576317173651</v>
+        <v>2117.966123631714</v>
       </c>
       <c r="F104" t="n">
-        <v>1327.408651990087</v>
+        <v>1169.255413566833</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2005</v>
+        <v>2017</v>
       </c>
       <c r="C105" t="n">
-        <v>331.5069213701777</v>
+        <v>258.0705993943514</v>
       </c>
       <c r="D105" t="n">
-        <v>6.203294989081905</v>
+        <v>6.676136012961517</v>
       </c>
       <c r="E105" t="n">
-        <v>1199.76142278193</v>
-      </c>
-      <c r="F105" t="n">
-        <v>1058.957153509448</v>
-      </c>
+        <v>2556.496479314575</v>
+      </c>
+      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="C106" t="n">
-        <v>460.1747583074363</v>
+        <v>311.7907018047362</v>
       </c>
       <c r="D106" t="n">
-        <v>11.64194336322395</v>
+        <v>11.58756978807228</v>
       </c>
       <c r="E106" t="n">
-        <v>2855.621291381434</v>
-      </c>
-      <c r="F106" t="n">
-        <v>1840.502628696817</v>
-      </c>
+        <v>6344.764701752276</v>
+      </c>
+      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="C107" t="n">
-        <v>488.7168621128653</v>
+        <v>346.7191883603683</v>
       </c>
       <c r="D107" t="n">
-        <v>15.93446799548587</v>
+        <v>23.03373067151695</v>
       </c>
       <c r="E107" t="n">
-        <v>3651.595676464933</v>
-      </c>
-      <c r="F107" t="n">
-        <v>1951.972736055409</v>
-      </c>
+        <v>10242.86875527961</v>
+      </c>
+      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="C108" t="n">
-        <v>258.4614254872664</v>
+        <v>313.2001009260769</v>
       </c>
       <c r="D108" t="n">
-        <v>7.607990773103028</v>
+        <v>8.551356125382863</v>
       </c>
       <c r="E108" t="n">
-        <v>1009.068659396665</v>
-      </c>
-      <c r="F108" t="inlineStr"/>
+        <v>1803.274423131739</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2844.543528890281</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="C109" t="n">
-        <v>362.5074356904787</v>
+        <v>309.2023526492062</v>
       </c>
       <c r="D109" t="n">
-        <v>11.41569863903253</v>
+        <v>8.112949745931397</v>
       </c>
       <c r="E109" t="n">
-        <v>1979.348480128897</v>
+        <v>4538.9274088344</v>
       </c>
       <c r="F109" t="n">
-        <v>1931.958235635961</v>
+        <v>2692.086141824332</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2012</v>
+        <v>1998</v>
       </c>
       <c r="C110" t="n">
-        <v>478.9121550379911</v>
+        <v>511.7779201959133</v>
       </c>
       <c r="D110" t="n">
-        <v>13.12749136781718</v>
+        <v>36.19501564136775</v>
       </c>
       <c r="E110" t="n">
-        <v>4949.73144092061</v>
+        <v>31282.05596369573</v>
       </c>
       <c r="F110" t="n">
-        <v>1819.587265486208</v>
+        <v>2324.342543692302</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2013</v>
+        <v>1999</v>
       </c>
       <c r="C111" t="n">
-        <v>378.3480399434748</v>
+        <v>472.7224528559897</v>
       </c>
       <c r="D111" t="n">
-        <v>10.12016989632461</v>
+        <v>48.50897211804379</v>
       </c>
       <c r="E111" t="n">
-        <v>2035.913680912662</v>
-      </c>
-      <c r="F111" t="inlineStr"/>
+        <v>42066.63358051859</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2991.150563315237</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2015</v>
+        <v>2000</v>
       </c>
       <c r="C112" t="n">
-        <v>497.7632988992286</v>
+        <v>658.0717263768403</v>
       </c>
       <c r="D112" t="n">
-        <v>7.786699080019884</v>
+        <v>149.0405328869568</v>
       </c>
       <c r="E112" t="n">
-        <v>1262.500187401904</v>
-      </c>
-      <c r="F112" t="n">
-        <v>2237.34591300376</v>
-      </c>
+        <v>125467.5183689415</v>
+      </c>
+      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="C113" t="n">
-        <v>411.0125285131361</v>
+        <v>331.4877721201903</v>
       </c>
       <c r="D113" t="n">
-        <v>6.800010880960264</v>
+        <v>50.18979259735507</v>
       </c>
       <c r="E113" t="n">
-        <v>1370.537290622364</v>
+        <v>44575.50652778852</v>
       </c>
       <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2018</v>
+        <v>2002</v>
       </c>
       <c r="C114" t="n">
-        <v>533.7648581136816</v>
+        <v>294.5415371642576</v>
       </c>
       <c r="D114" t="n">
-        <v>8.861400654563345</v>
+        <v>29.14598483225638</v>
       </c>
       <c r="E114" t="n">
-        <v>2120.977226055894</v>
+        <v>26665.21677702123</v>
       </c>
       <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2019</v>
+        <v>2004</v>
       </c>
       <c r="C115" t="n">
-        <v>718.6928880269085</v>
+        <v>506.2812781192748</v>
       </c>
       <c r="D115" t="n">
-        <v>14.56837974619557</v>
+        <v>37.49690548117942</v>
       </c>
       <c r="E115" t="n">
-        <v>3904.189299678584</v>
-      </c>
-      <c r="F115" t="n">
-        <v>2684.008110329993</v>
-      </c>
+        <v>34221.37857013181</v>
+      </c>
+      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2020</v>
+        <v>2005</v>
       </c>
       <c r="C116" t="n">
-        <v>806.7226348392613</v>
+        <v>316.7817410885504</v>
       </c>
       <c r="D116" t="n">
-        <v>34.40182519493672</v>
+        <v>25.30924364201172</v>
       </c>
       <c r="E116" t="n">
-        <v>10323.8091120662</v>
-      </c>
-      <c r="F116" t="n">
-        <v>3965.94600067507</v>
-      </c>
+        <v>18704.70590562527</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1998</v>
+        <v>2006</v>
       </c>
       <c r="C117" t="n">
-        <v>26.19358774329543</v>
+        <v>742.5659804690229</v>
       </c>
       <c r="D117" t="n">
-        <v>0.9487900488772769</v>
+        <v>38.98089422772803</v>
       </c>
       <c r="E117" t="n">
-        <v>402.6620547654516</v>
-      </c>
-      <c r="F117" t="n">
-        <v>48.97028627685659</v>
-      </c>
+        <v>38253.94476862722</v>
+      </c>
+      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1999</v>
+        <v>1980</v>
       </c>
       <c r="C118" t="n">
-        <v>23.29827186069571</v>
+        <v>505.5180966059012</v>
       </c>
       <c r="D118" t="n">
-        <v>1.294325316644074</v>
-      </c>
-      <c r="E118" t="n">
-        <v>1345.366631418203</v>
-      </c>
+        <v>21.15775274858974</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2000</v>
+        <v>1981</v>
       </c>
       <c r="C119" t="n">
-        <v>25.79900743700395</v>
+        <v>550.3758486272691</v>
       </c>
       <c r="D119" t="n">
-        <v>4.563323058370141</v>
+        <v>34.93460434676286</v>
       </c>
       <c r="E119" t="n">
-        <v>3775.021998105326</v>
-      </c>
-      <c r="F119" t="inlineStr"/>
+        <v>5632.526421804672</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1222.747684883211</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2001</v>
+        <v>1982</v>
       </c>
       <c r="C120" t="n">
-        <v>15.13990380878278</v>
+        <v>370.5516062726167</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9770348796895605</v>
+        <v>23.32581395234075</v>
       </c>
       <c r="E120" t="n">
-        <v>487.1923265162463</v>
-      </c>
-      <c r="F120" t="inlineStr"/>
+        <v>4967.043752943522</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1468.730551916253</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2002</v>
+        <v>1983</v>
       </c>
       <c r="C121" t="n">
-        <v>9.084978109991951</v>
+        <v>649.8509995284052</v>
       </c>
       <c r="D121" t="n">
-        <v>0.5705195102393636</v>
+        <v>40.53987019922116</v>
       </c>
       <c r="E121" t="n">
-        <v>323.1702910142598</v>
+        <v>15526.71588886437</v>
       </c>
       <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>2003</v>
+        <v>1987</v>
       </c>
       <c r="C122" t="n">
-        <v>17.46635450249664</v>
+        <v>676.6764336526682</v>
       </c>
       <c r="D122" t="n">
-        <v>0.6693553202864039</v>
-      </c>
-      <c r="E122" t="n">
-        <v>386.374054264836</v>
-      </c>
-      <c r="F122" t="inlineStr"/>
+        <v>86.82209565769185</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="n">
+        <v>2100.242447930635</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2004</v>
+        <v>1988</v>
       </c>
       <c r="C123" t="n">
-        <v>21.05577385199837</v>
-      </c>
-      <c r="D123" t="inlineStr"/>
+        <v>406.8379156336074</v>
+      </c>
+      <c r="D123" t="n">
+        <v>6.463634185600521</v>
+      </c>
       <c r="E123" t="n">
-        <v>360.7471070022716</v>
-      </c>
-      <c r="F123" t="inlineStr"/>
+        <v>5394.759924488313</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1956.35041097056</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2005</v>
+        <v>1989</v>
       </c>
       <c r="C124" t="n">
-        <v>11.14351197780905</v>
+        <v>511.3170949557855</v>
       </c>
       <c r="D124" t="n">
-        <v>0.6629085824922188</v>
+        <v>12.63927178839586</v>
       </c>
       <c r="E124" t="n">
-        <v>397.5642983594295</v>
-      </c>
-      <c r="F124" t="inlineStr"/>
+        <v>4460.441339471327</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1044.896885386453</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2006</v>
+        <v>1990</v>
       </c>
       <c r="C125" t="n">
-        <v>27.47665027735095</v>
+        <v>649.9202417294422</v>
       </c>
       <c r="D125" t="n">
-        <v>1.521026161180075</v>
+        <v>17.57738690046505</v>
       </c>
       <c r="E125" t="n">
-        <v>1237.383249154354</v>
-      </c>
-      <c r="F125" t="inlineStr"/>
+        <v>8214.948755565014</v>
+      </c>
+      <c r="F125" t="n">
+        <v>979.7220276811303</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2011</v>
+        <v>1991</v>
       </c>
       <c r="C126" t="n">
-        <v>17.73508657513642</v>
+        <v>778.7265232398832</v>
       </c>
       <c r="D126" t="n">
-        <v>2.016574622946294</v>
+        <v>10.38404257891497</v>
       </c>
       <c r="E126" t="n">
-        <v>1602.590247699093</v>
-      </c>
-      <c r="F126" t="n">
-        <v>61.47960654839287</v>
-      </c>
+        <v>4591.88857371901</v>
+      </c>
+      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>2012</v>
+        <v>1992</v>
       </c>
       <c r="C127" t="n">
-        <v>19.15234850763907</v>
+        <v>370.8779181844769</v>
       </c>
       <c r="D127" t="n">
-        <v>0.5138848656344245</v>
+        <v>6.347507473798679</v>
       </c>
       <c r="E127" t="n">
-        <v>232.6526434360104</v>
+        <v>2493.370999714289</v>
       </c>
       <c r="F127" t="n">
-        <v>66.41781727408723</v>
+        <v>938.677394480183</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2013</v>
+        <v>1993</v>
       </c>
       <c r="C128" t="n">
-        <v>12.5663757432522</v>
+        <v>472.877631237185</v>
       </c>
       <c r="D128" t="n">
-        <v>1.630946239459804</v>
+        <v>11.59048939228629</v>
       </c>
       <c r="E128" t="n">
-        <v>1160.383372960583</v>
+        <v>4019.524580910777</v>
       </c>
       <c r="F128" t="n">
-        <v>78.01115852755343</v>
+        <v>1367.368373150696</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2014</v>
+        <v>1994</v>
       </c>
       <c r="C129" t="n">
-        <v>18.796115657675</v>
+        <v>1085.256507357366</v>
       </c>
       <c r="D129" t="n">
-        <v>1.175029821313021</v>
+        <v>17.94727561707502</v>
       </c>
       <c r="E129" t="n">
-        <v>839.0213576492474</v>
+        <v>2806.311770386166</v>
       </c>
       <c r="F129" t="n">
-        <v>120.1697062133845</v>
+        <v>2028.655443525404</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2015</v>
+        <v>1995</v>
       </c>
       <c r="C130" t="n">
-        <v>17.5119324139581</v>
+        <v>509.7551644368058</v>
       </c>
       <c r="D130" t="n">
-        <v>0.8130548232730483</v>
+        <v>9.576232613433445</v>
       </c>
       <c r="E130" t="n">
-        <v>503.0080546341568</v>
+        <v>3225.053974292888</v>
       </c>
       <c r="F130" t="n">
-        <v>96.72534716871388</v>
+        <v>1232.042043959136</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2016</v>
+        <v>1996</v>
       </c>
       <c r="C131" t="n">
-        <v>11.70748200784629</v>
+        <v>499.3596956523585</v>
       </c>
       <c r="D131" t="n">
-        <v>1.454344307776128</v>
+        <v>6.996084150222485</v>
       </c>
       <c r="E131" t="n">
-        <v>1297.381876102844</v>
+        <v>2300.830588629901</v>
       </c>
       <c r="F131" t="n">
-        <v>76.04592931031137</v>
+        <v>815.4925754911436</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2018</v>
+        <v>1997</v>
       </c>
       <c r="C132" t="n">
-        <v>19.12681211802197</v>
+        <v>719.8730708974265</v>
       </c>
       <c r="D132" t="n">
-        <v>0.5349317088758103</v>
+        <v>12.93259490101161</v>
       </c>
       <c r="E132" t="n">
-        <v>323.0775189909162</v>
+        <v>4200.335831863231</v>
       </c>
       <c r="F132" t="n">
-        <v>73.09440190889266</v>
+        <v>1022.443871051485</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2019</v>
+        <v>1998</v>
       </c>
       <c r="C133" t="n">
-        <v>34.72392568011911</v>
+        <v>638.6742833177299</v>
       </c>
       <c r="D133" t="n">
-        <v>1.724874603309876</v>
+        <v>17.79439531362919</v>
       </c>
       <c r="E133" t="n">
-        <v>931.3024924336419</v>
+        <v>6204.300176263578</v>
       </c>
       <c r="F133" t="n">
-        <v>101.2192522507846</v>
+        <v>1320.302739733719</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2020</v>
+        <v>1999</v>
       </c>
       <c r="C134" t="n">
-        <v>27.32202220905914</v>
+        <v>623.1556853516021</v>
       </c>
       <c r="D134" t="n">
-        <v>0.9665635568388418</v>
+        <v>16.90767448409418</v>
       </c>
       <c r="E134" t="n">
-        <v>378.6150196456369</v>
+        <v>7079.726346128299</v>
       </c>
       <c r="F134" t="n">
-        <v>118.0285072034226</v>
+        <v>2127.784367944353</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1995</v>
+        <v>2000</v>
       </c>
       <c r="C135" t="n">
-        <v>51.84164880541291</v>
+        <v>820.6835736131554</v>
       </c>
       <c r="D135" t="n">
-        <v>1.513583546964058</v>
+        <v>37.23347712024713</v>
       </c>
       <c r="E135" t="n">
-        <v>516.6387494041873</v>
+        <v>17073.01088071766</v>
       </c>
       <c r="F135" t="n">
-        <v>217.4736289185775</v>
+        <v>3114.422018139068</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1996</v>
+        <v>2001</v>
       </c>
       <c r="C136" t="n">
-        <v>51.32869255300714</v>
+        <v>664.6564457996925</v>
       </c>
       <c r="D136" t="n">
-        <v>1.302319497896878</v>
+        <v>25.53768851400098</v>
       </c>
       <c r="E136" t="n">
-        <v>461.7498730216965</v>
+        <v>18626.20105913134</v>
       </c>
       <c r="F136" t="n">
-        <v>172.3546509152409</v>
+        <v>1772.998760300929</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="C137" t="n">
-        <v>36.94641780367524</v>
+        <v>857.7224085594355</v>
       </c>
       <c r="D137" t="n">
-        <v>1.394462246581433</v>
+        <v>10.34244300971466</v>
       </c>
       <c r="E137" t="n">
-        <v>514.1625749794155</v>
+        <v>2632.664145744585</v>
       </c>
       <c r="F137" t="n">
-        <v>154.4015341962478</v>
+        <v>1509.466717849222</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="C138" t="n">
-        <v>44.33338123436558</v>
+        <v>731.5229103605973</v>
       </c>
       <c r="D138" t="n">
-        <v>2.018880068421233</v>
+        <v>5.254392900864078</v>
       </c>
       <c r="E138" t="n">
-        <v>764.6211430482372</v>
+        <v>1937.873751400207</v>
       </c>
       <c r="F138" t="n">
-        <v>211.1150106649136</v>
+        <v>1091.024638202054</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="C139" t="n">
-        <v>73.0669833962864</v>
+        <v>482.8510458880432</v>
       </c>
       <c r="D139" t="n">
-        <v>3.928161541156698</v>
+        <v>9.483917002062677</v>
       </c>
       <c r="E139" t="n">
-        <v>1777.995616931064</v>
+        <v>1932.576317173651</v>
       </c>
       <c r="F139" t="n">
-        <v>398.6230901488487</v>
+        <v>1327.408651990087</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="C140" t="n">
-        <v>81.08685298733415</v>
+        <v>331.5069213701777</v>
       </c>
       <c r="D140" t="n">
-        <v>4.575242451471255</v>
+        <v>6.203294989081905</v>
       </c>
       <c r="E140" t="n">
-        <v>1516.492426408186</v>
+        <v>1199.76142278193</v>
       </c>
       <c r="F140" t="n">
-        <v>514.5068887583486</v>
+        <v>1058.957153509448</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="C141" t="n">
-        <v>52.60046673804597</v>
+        <v>460.1747583074363</v>
       </c>
       <c r="D141" t="n">
-        <v>1.879791656584253</v>
+        <v>11.64194336322395</v>
       </c>
       <c r="E141" t="n">
-        <v>413.5974622691346</v>
+        <v>2855.621291381434</v>
       </c>
       <c r="F141" t="n">
-        <v>269.6605906807495</v>
+        <v>1840.502628696817</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="C142" t="n">
-        <v>46.98357972821391</v>
+        <v>488.7168621128653</v>
       </c>
       <c r="D142" t="n">
-        <v>1.55609186909282</v>
+        <v>15.93446799548587</v>
       </c>
       <c r="E142" t="n">
-        <v>346.9096987821957</v>
+        <v>3651.595676464933</v>
       </c>
       <c r="F142" t="n">
-        <v>234.9791294590155</v>
+        <v>1951.972736055409</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="C143" t="n">
-        <v>71.11798056391461</v>
+        <v>258.4614254872664</v>
       </c>
       <c r="D143" t="n">
-        <v>1.795468440882586</v>
+        <v>7.607990773103028</v>
       </c>
       <c r="E143" t="n">
-        <v>283.9482960266221</v>
-      </c>
-      <c r="F143" t="n">
-        <v>224.4606244047468</v>
-      </c>
+        <v>1009.068659396665</v>
+      </c>
+      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="C144" t="n">
-        <v>48.3453393142058</v>
+        <v>362.5074356904787</v>
       </c>
       <c r="D144" t="n">
-        <v>1.408076894832172</v>
+        <v>11.41569863903253</v>
       </c>
       <c r="E144" t="n">
-        <v>210.1078245525255</v>
+        <v>1979.348480128897</v>
       </c>
       <c r="F144" t="n">
-        <v>214.3728662810618</v>
+        <v>1931.958235635961</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="C145" t="n">
-        <v>42.51518181802197</v>
+        <v>478.9121550379911</v>
       </c>
       <c r="D145" t="n">
-        <v>1.070816223518787</v>
+        <v>13.12749136781718</v>
       </c>
       <c r="E145" t="n">
-        <v>228.7452194164096</v>
+        <v>4949.73144092061</v>
       </c>
       <c r="F145" t="n">
-        <v>201.7093548952199</v>
+        <v>1819.587265486208</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="C146" t="n">
-        <v>86.58930336778015</v>
+        <v>378.3480399434748</v>
       </c>
       <c r="D146" t="n">
-        <v>2.775111487476079</v>
+        <v>10.12016989632461</v>
       </c>
       <c r="E146" t="n">
-        <v>620.7708397972081</v>
-      </c>
-      <c r="F146" t="n">
-        <v>378.1158362215797</v>
-      </c>
+        <v>2035.913680912662</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="C147" t="n">
-        <v>51.03087038571355</v>
+        <v>497.7632988992286</v>
       </c>
       <c r="D147" t="n">
-        <v>2.310571913754004</v>
+        <v>7.786699080019884</v>
       </c>
       <c r="E147" t="n">
-        <v>635.3668724685566</v>
+        <v>1262.500187401904</v>
       </c>
       <c r="F147" t="n">
-        <v>231.1346288061736</v>
+        <v>2237.34591300376</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2008</v>
+        <v>2017</v>
       </c>
       <c r="C148" t="n">
-        <v>71.08463207595749</v>
+        <v>411.0125285131361</v>
       </c>
       <c r="D148" t="n">
-        <v>3.262624411887761</v>
+        <v>6.800010880960264</v>
       </c>
       <c r="E148" t="n">
-        <v>872.3696768427416</v>
-      </c>
-      <c r="F148" t="n">
-        <v>386.2994711912046</v>
-      </c>
+        <v>1370.537290622364</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C149" t="n">
-        <v>48.86119952432888</v>
+        <v>533.7648581136816</v>
       </c>
       <c r="D149" t="n">
-        <v>1.919191832445285</v>
+        <v>8.861400654563345</v>
       </c>
       <c r="E149" t="n">
-        <v>600.7702486693747</v>
-      </c>
-      <c r="F149" t="n">
-        <v>202.4339888312778</v>
-      </c>
+        <v>2120.977226055894</v>
+      </c>
+      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C150" t="n">
-        <v>65.96510915715997</v>
+        <v>718.6928880269085</v>
       </c>
       <c r="D150" t="n">
-        <v>3.384693481256054</v>
+        <v>14.56837974619557</v>
       </c>
       <c r="E150" t="n">
-        <v>1227.398360769503</v>
+        <v>3904.189299678584</v>
       </c>
       <c r="F150" t="n">
-        <v>369.7599024082867</v>
+        <v>2684.008110329993</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C151" t="n">
-        <v>56.57204888977957</v>
+        <v>806.7226348392613</v>
       </c>
       <c r="D151" t="n">
-        <v>2.832780406134927</v>
+        <v>34.40182519493672</v>
       </c>
       <c r="E151" t="n">
-        <v>972.1925805245899</v>
+        <v>10323.8091120662</v>
       </c>
       <c r="F151" t="n">
-        <v>341.0640154150917</v>
+        <v>3965.94600067507</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2013</v>
+        <v>1998</v>
       </c>
       <c r="C152" t="n">
-        <v>63.48898694135619</v>
+        <v>26.19358774329543</v>
       </c>
       <c r="D152" t="n">
-        <v>3.855099191699822</v>
+        <v>0.9487900488772769</v>
       </c>
       <c r="E152" t="n">
-        <v>1168.07009128708</v>
+        <v>402.6620547654516</v>
       </c>
       <c r="F152" t="n">
-        <v>351.499204803872</v>
+        <v>48.97028627685659</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2015</v>
+        <v>1999</v>
       </c>
       <c r="C153" t="n">
-        <v>57.01416403782338</v>
+        <v>23.29827186069571</v>
       </c>
       <c r="D153" t="n">
-        <v>2.391348098459219</v>
+        <v>1.294325316644074</v>
       </c>
       <c r="E153" t="n">
-        <v>754.0491003320777</v>
-      </c>
-      <c r="F153" t="n">
-        <v>409.839000549816</v>
-      </c>
+        <v>1345.366631418203</v>
+      </c>
+      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2016</v>
+        <v>2000</v>
       </c>
       <c r="C154" t="n">
-        <v>43.9130731820722</v>
+        <v>25.79900743700395</v>
       </c>
       <c r="D154" t="n">
-        <v>2.287241252932952</v>
+        <v>4.563323058370141</v>
       </c>
       <c r="E154" t="n">
-        <v>1125.197397706622</v>
-      </c>
-      <c r="F154" t="n">
-        <v>317.05013576509</v>
-      </c>
+        <v>3775.021998105326</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="C155" t="n">
-        <v>44.95639621018385</v>
+        <v>15.13990380878278</v>
       </c>
       <c r="D155" t="n">
-        <v>1.803022434623602</v>
+        <v>0.9770348796895605</v>
       </c>
       <c r="E155" t="n">
-        <v>515.2101754272189</v>
+        <v>487.1923265162463</v>
       </c>
       <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2018</v>
+        <v>2002</v>
       </c>
       <c r="C156" t="n">
-        <v>64.92423870709464</v>
+        <v>9.084978109991951</v>
       </c>
       <c r="D156" t="n">
-        <v>1.877982072012848</v>
+        <v>0.5705195102393636</v>
       </c>
       <c r="E156" t="n">
-        <v>554.3333338986376</v>
+        <v>323.1702910142598</v>
       </c>
       <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2019</v>
+        <v>2003</v>
       </c>
       <c r="C157" t="n">
-        <v>80.50937677145238</v>
+        <v>17.46635450249664</v>
       </c>
       <c r="D157" t="n">
-        <v>2.968824204243413</v>
+        <v>0.6693553202864039</v>
       </c>
       <c r="E157" t="n">
-        <v>954.5661575461341</v>
-      </c>
-      <c r="F157" t="n">
-        <v>524.4754086238461</v>
-      </c>
+        <v>386.374054264836</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2020</v>
+        <v>2004</v>
       </c>
       <c r="C158" t="n">
-        <v>71.8372376897468</v>
-      </c>
-      <c r="D158" t="n">
-        <v>3.80712212517937</v>
-      </c>
+        <v>21.05577385199837</v>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
-        <v>1344.798958664718</v>
-      </c>
-      <c r="F158" t="n">
-        <v>583.808114874567</v>
-      </c>
+        <v>360.7471070022716</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2022</v>
+        <v>2005</v>
       </c>
       <c r="C159" t="n">
-        <v>52.97632457821645</v>
+        <v>11.14351197780905</v>
       </c>
       <c r="D159" t="n">
-        <v>2.427926156380575</v>
+        <v>0.6629085824922188</v>
       </c>
       <c r="E159" t="n">
-        <v>342.3730570790243</v>
-      </c>
-      <c r="F159" t="n">
-        <v>256.7616142475802</v>
-      </c>
+        <v>397.5642983594295</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2023</v>
+        <v>2006</v>
       </c>
       <c r="C160" t="n">
-        <v>69.60689192687042</v>
+        <v>27.47665027735095</v>
       </c>
       <c r="D160" t="n">
-        <v>4.779546934824506</v>
+        <v>1.521026161180075</v>
       </c>
       <c r="E160" t="n">
-        <v>1242.637005193451</v>
-      </c>
-      <c r="F160" t="n">
-        <v>792.9255745199064</v>
-      </c>
+        <v>1237.383249154354</v>
+      </c>
+      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="C161" t="n">
-        <v>56.80154818167514</v>
+        <v>17.73508657513642</v>
       </c>
       <c r="D161" t="n">
-        <v>2.3578428964429</v>
+        <v>2.016574622946294</v>
       </c>
       <c r="E161" t="n">
-        <v>638.0967113674089</v>
+        <v>1602.590247699093</v>
       </c>
       <c r="F161" t="n">
-        <v>522.4665848434929</v>
+        <v>61.47960654839287</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C162" t="n">
-        <v>53.87233548816253</v>
+        <v>19.15234850763907</v>
       </c>
       <c r="D162" t="n">
-        <v>2.345286742713334</v>
+        <v>0.5138848656344245</v>
       </c>
       <c r="E162" t="n">
-        <v>932.5339464406246</v>
+        <v>232.6526434360104</v>
       </c>
       <c r="F162" t="n">
-        <v>642.2978201000033</v>
+        <v>66.41781727408723</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C163" t="n">
-        <v>104.2016310327637</v>
+        <v>12.5663757432522</v>
       </c>
       <c r="D163" t="n">
-        <v>2.714459331390005</v>
+        <v>1.630946239459804</v>
       </c>
       <c r="E163" t="n">
-        <v>1240.93973498854</v>
+        <v>1160.383372960583</v>
       </c>
       <c r="F163" t="n">
-        <v>824.898470910499</v>
+        <v>78.01115852755343</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C164" t="n">
-        <v>137.9310563440462</v>
+        <v>18.796115657675</v>
       </c>
       <c r="D164" t="n">
-        <v>3.857625945522277</v>
+        <v>1.175029821313021</v>
       </c>
       <c r="E164" t="n">
-        <v>1711.925508039553</v>
+        <v>839.0213576492474</v>
       </c>
       <c r="F164" t="n">
-        <v>1074.948130445055</v>
+        <v>120.1697062133845</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C165" t="n">
-        <v>134.4611208307123</v>
+        <v>17.5119324139581</v>
       </c>
       <c r="D165" t="n">
-        <v>10.24019644679919</v>
+        <v>0.8130548232730483</v>
       </c>
       <c r="E165" t="n">
-        <v>5531.287031060498</v>
+        <v>503.0080546341568</v>
       </c>
       <c r="F165" t="n">
-        <v>1391.548701768331</v>
+        <v>96.72534716871388</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C166" t="n">
-        <v>84.95532074240312</v>
+        <v>11.70748200784629</v>
       </c>
       <c r="D166" t="n">
-        <v>6.965005449565357</v>
+        <v>1.454344307776128</v>
       </c>
       <c r="E166" t="n">
-        <v>5211.151361561927</v>
+        <v>1297.381876102844</v>
       </c>
       <c r="F166" t="n">
-        <v>742.161384344123</v>
+        <v>76.04592931031137</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C167" t="n">
-        <v>35.46365198491126</v>
+        <v>19.12681211802197</v>
       </c>
       <c r="D167" t="n">
-        <v>1.133785265128868</v>
+        <v>0.5349317088758103</v>
       </c>
       <c r="E167" t="n">
-        <v>309.2847999129718</v>
+        <v>323.0775189909162</v>
       </c>
       <c r="F167" t="n">
-        <v>379.8833242881275</v>
+        <v>73.09440190889266</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C168" t="n">
-        <v>94.8917919305665</v>
+        <v>34.72392568011911</v>
       </c>
       <c r="D168" t="n">
-        <v>6.514171127915957</v>
+        <v>1.724874603309876</v>
       </c>
       <c r="E168" t="n">
-        <v>4459.477691870663</v>
+        <v>931.3024924336419</v>
       </c>
       <c r="F168" t="n">
-        <v>1196.258254404701</v>
+        <v>101.2192522507846</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C169" t="n">
-        <v>79.31336921214933</v>
+        <v>27.32202220905914</v>
       </c>
       <c r="D169" t="n">
-        <v>4.28544262902544</v>
+        <v>0.9665635568388418</v>
       </c>
       <c r="E169" t="n">
-        <v>3661.801282330153</v>
+        <v>378.6150196456369</v>
       </c>
       <c r="F169" t="n">
-        <v>645.3944124305115</v>
+        <v>118.0285072034226</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>2017</v>
+        <v>1995</v>
       </c>
       <c r="C170" t="n">
-        <v>9.184002099207618</v>
+        <v>51.84164880541291</v>
       </c>
       <c r="D170" t="n">
-        <v>0.3588019396451147</v>
+        <v>1.513583546964058</v>
       </c>
       <c r="E170" t="n">
-        <v>102.0178677716435</v>
+        <v>516.6387494041873</v>
       </c>
       <c r="F170" t="n">
-        <v>124.792395701237</v>
+        <v>217.4736289185775</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>2018</v>
+        <v>1996</v>
       </c>
       <c r="C171" t="n">
-        <v>14.44759731788683</v>
+        <v>51.32869255300714</v>
       </c>
       <c r="D171" t="n">
-        <v>0.3874645503031524</v>
+        <v>1.302319497896878</v>
       </c>
       <c r="E171" t="n">
-        <v>176.9669915686676</v>
+        <v>461.7498730216965</v>
       </c>
       <c r="F171" t="n">
-        <v>158.5439033355878</v>
+        <v>172.3546509152409</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>2019</v>
+        <v>1997</v>
       </c>
       <c r="C172" t="n">
-        <v>18.78688124727843</v>
+        <v>36.94641780367524</v>
       </c>
       <c r="D172" t="n">
-        <v>0.6178901518620976</v>
+        <v>1.394462246581433</v>
       </c>
       <c r="E172" t="n">
-        <v>264.5183551721593</v>
+        <v>514.1625749794155</v>
       </c>
       <c r="F172" t="n">
-        <v>233.6343973396616</v>
+        <v>154.4015341962478</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>2020</v>
+        <v>1998</v>
       </c>
       <c r="C173" t="n">
-        <v>21.67244455386674</v>
+        <v>44.33338123436558</v>
       </c>
       <c r="D173" t="n">
-        <v>1.309453396994647</v>
+        <v>2.018880068421233</v>
       </c>
       <c r="E173" t="n">
-        <v>749.0986577889029</v>
+        <v>764.6211430482372</v>
       </c>
       <c r="F173" t="n">
-        <v>313.0517725462432</v>
+        <v>211.1150106649136</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>2021</v>
+        <v>1999</v>
       </c>
       <c r="C174" t="n">
-        <v>14.30312637310008</v>
+        <v>73.0669833962864</v>
       </c>
       <c r="D174" t="n">
-        <v>0.5422665746753212</v>
+        <v>3.928161541156698</v>
       </c>
       <c r="E174" t="n">
-        <v>214.1688182808587</v>
+        <v>1777.995616931064</v>
       </c>
       <c r="F174" t="n">
-        <v>165.7129772392721</v>
+        <v>398.6230901488487</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2022</v>
+        <v>2000</v>
       </c>
       <c r="C175" t="n">
-        <v>5.744091848557019</v>
+        <v>81.08685298733415</v>
       </c>
       <c r="D175" t="n">
-        <v>0.1851848216557226</v>
+        <v>4.575242451471255</v>
       </c>
       <c r="E175" t="n">
-        <v>47.88008900768768</v>
+        <v>1516.492426408186</v>
       </c>
       <c r="F175" t="n">
-        <v>80.78150401352812</v>
+        <v>514.5068887583486</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>2023</v>
+        <v>2001</v>
       </c>
       <c r="C176" t="n">
-        <v>15.04784848792289</v>
+        <v>52.60046673804597</v>
       </c>
       <c r="D176" t="n">
-        <v>0.6394552042317473</v>
+        <v>1.879791656584253</v>
       </c>
       <c r="E176" t="n">
-        <v>510.9200881859394</v>
+        <v>413.5974622691346</v>
       </c>
       <c r="F176" t="n">
-        <v>230.7317320020855</v>
+        <v>269.6605906807495</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>2024</v>
+        <v>2002</v>
       </c>
       <c r="C177" t="n">
-        <v>14.06433535145543</v>
+        <v>46.98357972821391</v>
       </c>
       <c r="D177" t="n">
-        <v>0.670718985936172</v>
+        <v>1.55609186909282</v>
       </c>
       <c r="E177" t="n">
-        <v>216.0726392431546</v>
+        <v>346.9096987821957</v>
       </c>
       <c r="F177" t="n">
-        <v>195.8554627484408</v>
+        <v>234.9791294590155</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C178" t="n">
-        <v>40.49770628054306</v>
+        <v>71.11798056391461</v>
       </c>
       <c r="D178" t="n">
-        <v>1.568285017308244</v>
+        <v>1.795468440882586</v>
       </c>
       <c r="E178" t="n">
-        <v>301.6589137078369</v>
-      </c>
-      <c r="F178" t="inlineStr"/>
+        <v>283.9482960266221</v>
+      </c>
+      <c r="F178" t="n">
+        <v>224.4606244047468</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="C179" t="n">
-        <v>54.96876275821803</v>
+        <v>48.3453393142058</v>
       </c>
       <c r="D179" t="n">
-        <v>1.851338944135336</v>
+        <v>1.408076894832172</v>
       </c>
       <c r="E179" t="n">
-        <v>1311.492749597605</v>
-      </c>
-      <c r="F179" t="inlineStr"/>
+        <v>210.1078245525255</v>
+      </c>
+      <c r="F179" t="n">
+        <v>214.3728662810618</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="C180" t="n">
-        <v>60.99075076540651</v>
+        <v>42.51518181802197</v>
       </c>
       <c r="D180" t="n">
-        <v>2.133795557464769</v>
+        <v>1.070816223518787</v>
       </c>
       <c r="E180" t="n">
-        <v>503.1664606147037</v>
-      </c>
-      <c r="F180" t="inlineStr"/>
+        <v>228.7452194164096</v>
+      </c>
+      <c r="F180" t="n">
+        <v>201.7093548952199</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="C181" t="n">
-        <v>40.95647110770329</v>
+        <v>86.58930336778015</v>
       </c>
       <c r="D181" t="n">
-        <v>1.252879391873128</v>
+        <v>2.775111487476079</v>
       </c>
       <c r="E181" t="n">
-        <v>329.1048795140786</v>
-      </c>
-      <c r="F181" t="inlineStr"/>
+        <v>620.7708397972081</v>
+      </c>
+      <c r="F181" t="n">
+        <v>378.1158362215797</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="C182" t="n">
-        <v>38.9613179373606</v>
+        <v>51.03087038571355</v>
       </c>
       <c r="D182" t="n">
-        <v>2.236296430197122</v>
+        <v>2.310571913754004</v>
       </c>
       <c r="E182" t="n">
-        <v>670.5508169593893</v>
-      </c>
-      <c r="F182" t="inlineStr"/>
+        <v>635.3668724685566</v>
+      </c>
+      <c r="F182" t="n">
+        <v>231.1346288061736</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C183" t="n">
-        <v>61.24746583145092</v>
+        <v>71.08463207595749</v>
       </c>
       <c r="D183" t="n">
-        <v>5.805716563483374</v>
+        <v>3.262624411887761</v>
       </c>
       <c r="E183" t="n">
-        <v>1622.063444642838</v>
-      </c>
-      <c r="F183" t="inlineStr"/>
+        <v>872.3696768427416</v>
+      </c>
+      <c r="F183" t="n">
+        <v>386.2994711912046</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C184" t="n">
-        <v>47.91701063717161</v>
+        <v>48.86119952432888</v>
       </c>
       <c r="D184" t="n">
-        <v>2.515902984650999</v>
+        <v>1.919191832445285</v>
       </c>
       <c r="E184" t="n">
-        <v>889.3250659510968</v>
-      </c>
-      <c r="F184" t="inlineStr"/>
+        <v>600.7702486693747</v>
+      </c>
+      <c r="F184" t="n">
+        <v>202.4339888312778</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C185" t="n">
-        <v>39.05192646536998</v>
+        <v>65.96510915715997</v>
       </c>
       <c r="D185" t="n">
-        <v>1.398696054096747</v>
+        <v>3.384693481256054</v>
       </c>
       <c r="E185" t="n">
-        <v>380.8111625026891</v>
-      </c>
-      <c r="F185" t="inlineStr"/>
+        <v>1227.398360769503</v>
+      </c>
+      <c r="F185" t="n">
+        <v>369.7599024082867</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C186" t="n">
-        <v>50.20948995881738</v>
+        <v>56.57204888977957</v>
       </c>
       <c r="D186" t="n">
-        <v>2.038242383544368</v>
+        <v>2.832780406134927</v>
       </c>
       <c r="E186" t="n">
-        <v>549.9889067958491</v>
-      </c>
-      <c r="F186" t="inlineStr"/>
+        <v>972.1925805245899</v>
+      </c>
+      <c r="F186" t="n">
+        <v>341.0640154150917</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C187" t="n">
-        <v>34.69544946503871</v>
+        <v>63.48898694135619</v>
       </c>
       <c r="D187" t="n">
-        <v>1.457104115371196</v>
+        <v>3.855099191699822</v>
       </c>
       <c r="E187" t="n">
-        <v>697.9424621322642</v>
-      </c>
-      <c r="F187" t="inlineStr"/>
+        <v>1168.07009128708</v>
+      </c>
+      <c r="F187" t="n">
+        <v>351.499204803872</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C188" t="n">
-        <v>42.80987836444336</v>
+        <v>57.01416403782338</v>
       </c>
       <c r="D188" t="n">
-        <v>2.138527272582623</v>
+        <v>2.391348098459219</v>
       </c>
       <c r="E188" t="n">
-        <v>624.6852016966637</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
+        <v>754.0491003320777</v>
+      </c>
+      <c r="F188" t="n">
+        <v>409.839000549816</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C189" t="n">
-        <v>29.42956641402305</v>
+        <v>43.9130731820722</v>
       </c>
       <c r="D189" t="n">
-        <v>0.8405232956842483</v>
+        <v>2.287241252932952</v>
       </c>
       <c r="E189" t="n">
-        <v>369.2203856387403</v>
-      </c>
-      <c r="F189" t="inlineStr"/>
+        <v>1125.197397706622</v>
+      </c>
+      <c r="F189" t="n">
+        <v>317.05013576509</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
+          <t>002-46599</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C190" t="n">
+        <v>44.95639621018385</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1.803022434623602</v>
+      </c>
+      <c r="E190" t="n">
+        <v>515.2101754272189</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>002-46599</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C191" t="n">
+        <v>64.92423870709464</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1.877982072012848</v>
+      </c>
+      <c r="E191" t="n">
+        <v>554.3333338986376</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>002-46599</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C192" t="n">
+        <v>80.50937677145238</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2.968824204243413</v>
+      </c>
+      <c r="E192" t="n">
+        <v>954.5661575461341</v>
+      </c>
+      <c r="F192" t="n">
+        <v>524.4754086238461</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>002-46599</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C193" t="n">
+        <v>71.8372376897468</v>
+      </c>
+      <c r="D193" t="n">
+        <v>3.80712212517937</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1344.798958664718</v>
+      </c>
+      <c r="F193" t="n">
+        <v>583.808114874567</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>002-46599</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C194" t="n">
+        <v>52.97632457821645</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2.427926156380575</v>
+      </c>
+      <c r="E194" t="n">
+        <v>342.3730570790243</v>
+      </c>
+      <c r="F194" t="n">
+        <v>256.7616142475802</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>002-46599</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C195" t="n">
+        <v>69.60689192687042</v>
+      </c>
+      <c r="D195" t="n">
+        <v>4.779546934824506</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1242.637005193451</v>
+      </c>
+      <c r="F195" t="n">
+        <v>792.9255745199064</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>002-46599</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C196" t="n">
+        <v>56.80154818167514</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2.3578428964429</v>
+      </c>
+      <c r="E196" t="n">
+        <v>638.0967113674089</v>
+      </c>
+      <c r="F196" t="n">
+        <v>522.4665848434929</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>002-60929</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C197" t="n">
+        <v>53.87233548816253</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2.345286742713334</v>
+      </c>
+      <c r="E197" t="n">
+        <v>932.5339464406246</v>
+      </c>
+      <c r="F197" t="n">
+        <v>642.2978201000033</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>002-60929</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C198" t="n">
+        <v>104.2016310327637</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2.714459331390005</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1240.93973498854</v>
+      </c>
+      <c r="F198" t="n">
+        <v>824.898470910499</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>002-60929</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C199" t="n">
+        <v>137.9310563440462</v>
+      </c>
+      <c r="D199" t="n">
+        <v>3.857625945522277</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1711.925508039553</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1074.948130445055</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>002-60929</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C200" t="n">
+        <v>134.4611208307123</v>
+      </c>
+      <c r="D200" t="n">
+        <v>10.24019644679919</v>
+      </c>
+      <c r="E200" t="n">
+        <v>5531.287031060498</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1391.548701768331</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>002-60929</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C201" t="n">
+        <v>84.95532074240312</v>
+      </c>
+      <c r="D201" t="n">
+        <v>6.965005449565357</v>
+      </c>
+      <c r="E201" t="n">
+        <v>5211.151361561927</v>
+      </c>
+      <c r="F201" t="n">
+        <v>742.161384344123</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>002-60929</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C202" t="n">
+        <v>35.46365198491126</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1.133785265128868</v>
+      </c>
+      <c r="E202" t="n">
+        <v>309.2847999129718</v>
+      </c>
+      <c r="F202" t="n">
+        <v>379.8833242881275</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>002-60929</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C203" t="n">
+        <v>94.8917919305665</v>
+      </c>
+      <c r="D203" t="n">
+        <v>6.514171127915957</v>
+      </c>
+      <c r="E203" t="n">
+        <v>4459.477691870663</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1196.258254404701</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>002-60929</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C204" t="n">
+        <v>79.31336921214933</v>
+      </c>
+      <c r="D204" t="n">
+        <v>4.28544262902544</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3661.801282330153</v>
+      </c>
+      <c r="F204" t="n">
+        <v>645.3944124305115</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>002-60933</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C205" t="n">
+        <v>9.184002099207618</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.3588019396451147</v>
+      </c>
+      <c r="E205" t="n">
+        <v>102.0178677716435</v>
+      </c>
+      <c r="F205" t="n">
+        <v>124.792395701237</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>002-60933</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C206" t="n">
+        <v>14.44759731788683</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.3874645503031524</v>
+      </c>
+      <c r="E206" t="n">
+        <v>176.9669915686676</v>
+      </c>
+      <c r="F206" t="n">
+        <v>158.5439033355878</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>002-60933</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C207" t="n">
+        <v>18.78688124727843</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.6178901518620976</v>
+      </c>
+      <c r="E207" t="n">
+        <v>264.5183551721593</v>
+      </c>
+      <c r="F207" t="n">
+        <v>233.6343973396616</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>002-60933</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C208" t="n">
+        <v>21.67244455386674</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1.309453396994647</v>
+      </c>
+      <c r="E208" t="n">
+        <v>749.0986577889029</v>
+      </c>
+      <c r="F208" t="n">
+        <v>313.0517725462432</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>002-60933</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C209" t="n">
+        <v>14.30312637310008</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.5422665746753212</v>
+      </c>
+      <c r="E209" t="n">
+        <v>214.1688182808587</v>
+      </c>
+      <c r="F209" t="n">
+        <v>165.7129772392721</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>002-60933</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C210" t="n">
+        <v>5.744091848557019</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.1851848216557226</v>
+      </c>
+      <c r="E210" t="n">
+        <v>47.88008900768768</v>
+      </c>
+      <c r="F210" t="n">
+        <v>80.78150401352812</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>002-60933</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C211" t="n">
+        <v>15.04784848792289</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.6394552042317473</v>
+      </c>
+      <c r="E211" t="n">
+        <v>510.9200881859394</v>
+      </c>
+      <c r="F211" t="n">
+        <v>230.7317320020855</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>002-60933</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C212" t="n">
+        <v>14.06433535145543</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.670718985936172</v>
+      </c>
+      <c r="E212" t="n">
+        <v>216.0726392431546</v>
+      </c>
+      <c r="F212" t="n">
+        <v>195.8554627484408</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
           <t>002-63540</t>
         </is>
       </c>
-      <c r="B190" t="n">
+      <c r="B213" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C213" t="n">
+        <v>40.49770628054306</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1.568285017308244</v>
+      </c>
+      <c r="E213" t="n">
+        <v>301.6589137078369</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C214" t="n">
+        <v>54.96876275821803</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1.851338944135336</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1311.492749597605</v>
+      </c>
+      <c r="F214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C215" t="n">
+        <v>60.99075076540651</v>
+      </c>
+      <c r="D215" t="n">
+        <v>2.133795557464769</v>
+      </c>
+      <c r="E215" t="n">
+        <v>503.1664606147037</v>
+      </c>
+      <c r="F215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C216" t="n">
+        <v>40.95647110770329</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1.252879391873128</v>
+      </c>
+      <c r="E216" t="n">
+        <v>329.1048795140786</v>
+      </c>
+      <c r="F216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C217" t="n">
+        <v>38.9613179373606</v>
+      </c>
+      <c r="D217" t="n">
+        <v>2.236296430197122</v>
+      </c>
+      <c r="E217" t="n">
+        <v>670.5508169593893</v>
+      </c>
+      <c r="F217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C218" t="n">
+        <v>61.24746583145092</v>
+      </c>
+      <c r="D218" t="n">
+        <v>5.805716563483374</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1622.063444642838</v>
+      </c>
+      <c r="F218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C219" t="n">
+        <v>47.91701063717161</v>
+      </c>
+      <c r="D219" t="n">
+        <v>2.515902984650999</v>
+      </c>
+      <c r="E219" t="n">
+        <v>889.3250659510968</v>
+      </c>
+      <c r="F219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C220" t="n">
+        <v>39.05192646536998</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1.398696054096747</v>
+      </c>
+      <c r="E220" t="n">
+        <v>380.8111625026891</v>
+      </c>
+      <c r="F220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C221" t="n">
+        <v>50.20948995881738</v>
+      </c>
+      <c r="D221" t="n">
+        <v>2.038242383544368</v>
+      </c>
+      <c r="E221" t="n">
+        <v>549.9889067958491</v>
+      </c>
+      <c r="F221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C222" t="n">
+        <v>34.69544946503871</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1.457104115371196</v>
+      </c>
+      <c r="E222" t="n">
+        <v>697.9424621322642</v>
+      </c>
+      <c r="F222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C223" t="n">
+        <v>42.80987836444336</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2.138527272582623</v>
+      </c>
+      <c r="E223" t="n">
+        <v>624.6852016966637</v>
+      </c>
+      <c r="F223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C224" t="n">
+        <v>29.42956641402305</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.8405232956842483</v>
+      </c>
+      <c r="E224" t="n">
+        <v>369.2203856387403</v>
+      </c>
+      <c r="F224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
         <v>2019</v>
       </c>
-      <c r="C190" t="n">
+      <c r="C225" t="n">
         <v>103.9758223784085</v>
       </c>
-      <c r="D190" t="n">
+      <c r="D225" t="n">
         <v>13.14216228483046</v>
       </c>
-      <c r="E190" t="n">
+      <c r="E225" t="n">
         <v>1037.211966257285</v>
       </c>
-      <c r="F190" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4520,7 +5270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4930,17 +5680,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nitelva</t>
+          <t>Leira</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kjellerholen Nitelva (N6)</t>
+          <t>Frogner Leira</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4955,36 +5705,36 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>increasing</t>
+          <t>no trend</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.003160052923044443</v>
+        <v>0.1640010416143751</v>
       </c>
       <c r="H10" t="n">
-        <v>3.470933881348371</v>
+        <v>2.475512890470671</v>
       </c>
       <c r="I10" t="n">
-        <v>4.593435017721163</v>
+        <v>5.408632607562659</v>
       </c>
       <c r="J10" t="n">
-        <v>1.944762213624923</v>
+        <v>-0.9369084125057472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nitelva</t>
+          <t>Leira</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kjellerholen Nitelva (N6)</t>
+          <t>Frogner Leira</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5003,32 +5753,32 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.3333582434882612</v>
+        <v>0.06486517886852883</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07407270716835131</v>
+        <v>-0.6790897311063885</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2950521819305871</v>
+        <v>0.1131140360397112</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1045390975099419</v>
+        <v>-1.688669321656807</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nitelva</t>
+          <t>Leira</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kjellerholen Nitelva (N6)</t>
+          <t>Frogner Leira</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5047,32 +5797,32 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.5030370130775135</v>
+        <v>0.08545429152509176</v>
       </c>
       <c r="H12" t="n">
-        <v>43.99227185463047</v>
+        <v>-642.9061890724033</v>
       </c>
       <c r="I12" t="n">
-        <v>166.1441637751303</v>
+        <v>54.00705106536475</v>
       </c>
       <c r="J12" t="n">
-        <v>-57.0336519296224</v>
+        <v>-1466.234107504659</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nitelva</t>
+          <t>Leira</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kjellerholen Nitelva (N6)</t>
+          <t>Frogner Leira</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5091,32 +5841,32 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.00123327446599264</v>
+        <v>0.03709735848582496</v>
       </c>
       <c r="H13" t="n">
-        <v>41.01672239809476</v>
+        <v>40.53582973070269</v>
       </c>
       <c r="I13" t="n">
-        <v>66.32065936035454</v>
+        <v>69.3172273800068</v>
       </c>
       <c r="J13" t="n">
-        <v>17.9801883906638</v>
+        <v>2.647169555182427</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Leira</t>
+          <t>Nitelva</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Leira ved Leirsund (L8)</t>
+          <t>Kjellerholen Nitelva (N6)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5131,36 +5881,36 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>no trend</t>
+          <t>increasing</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.9015386266571279</v>
+        <v>0.003160052923044443</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.296307385341535</v>
+        <v>3.470933881348371</v>
       </c>
       <c r="I14" t="n">
-        <v>82.21564166976651</v>
+        <v>4.593435017721163</v>
       </c>
       <c r="J14" t="n">
-        <v>-60.09671602524102</v>
+        <v>1.944762213624923</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Leira</t>
+          <t>Nitelva</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Leira ved Leirsund (L8)</t>
+          <t>Kjellerholen Nitelva (N6)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5179,32 +5929,32 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.5361867719001741</v>
+        <v>0.3333582434882612</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.658683993950066</v>
+        <v>0.07407270716835131</v>
       </c>
       <c r="I15" t="n">
-        <v>4.17546032446152</v>
+        <v>0.2950521819305871</v>
       </c>
       <c r="J15" t="n">
-        <v>-18.34327310987147</v>
+        <v>-0.1045390975099419</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Leira</t>
+          <t>Nitelva</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Leira ved Leirsund (L8)</t>
+          <t>Kjellerholen Nitelva (N6)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5223,32 +5973,32 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.5361867719001741</v>
+        <v>0.5030370130775135</v>
       </c>
       <c r="H16" t="n">
-        <v>-1416.681676954807</v>
+        <v>43.99227185463047</v>
       </c>
       <c r="I16" t="n">
-        <v>3778.08089655529</v>
+        <v>166.1441637751303</v>
       </c>
       <c r="J16" t="n">
-        <v>-15516.67266450654</v>
+        <v>-57.0336519296224</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Leira</t>
+          <t>Nitelva</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leira ved Leirsund (L8)</t>
+          <t>Kjellerholen Nitelva (N6)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5263,41 +6013,41 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>no trend</t>
+          <t>increasing</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0.00123327446599264</v>
       </c>
       <c r="H17" t="n">
-        <v>666.8080196229348</v>
+        <v>41.01672239809476</v>
       </c>
       <c r="I17" t="n">
-        <v>666.8080196229348</v>
+        <v>66.32065936035454</v>
       </c>
       <c r="J17" t="n">
-        <v>666.8080196229348</v>
+        <v>17.9801883906638</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nitelva</t>
+          <t>Leira</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rud Nitelva (N8)</t>
+          <t>Leira ved Leirsund (L8)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>Slightly upstream</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5311,37 +6061,37 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.6780801094706033</v>
+        <v>0.9015386266571279</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.801876395855551</v>
+        <v>-2.296307385341535</v>
       </c>
       <c r="I18" t="n">
-        <v>4.544817532317254</v>
+        <v>82.21564166976651</v>
       </c>
       <c r="J18" t="n">
-        <v>-6.262280431226346</v>
+        <v>-60.09671602524102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nitelva</t>
+          <t>Leira</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rud Nitelva (N8)</t>
+          <t>Leira ved Leirsund (L8)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>Slightly upstream</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5355,37 +6105,37 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.05775818863725046</v>
+        <v>0.5361867719001741</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2079202265961669</v>
+        <v>-1.658683993950066</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01299309778703766</v>
+        <v>4.17546032446152</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4864098227719608</v>
+        <v>-18.34327310987147</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nitelva</t>
+          <t>Leira</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rud Nitelva (N8)</t>
+          <t>Leira ved Leirsund (L8)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>Slightly upstream</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5395,41 +6145,41 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>decreasing</t>
+          <t>no trend</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.0130971254873018</v>
+        <v>0.5361867719001741</v>
       </c>
       <c r="H20" t="n">
-        <v>-97.31040128260565</v>
+        <v>-1416.681676954807</v>
       </c>
       <c r="I20" t="n">
-        <v>-28.55560601376133</v>
+        <v>3778.08089655529</v>
       </c>
       <c r="J20" t="n">
-        <v>-153.0466569291263</v>
+        <v>-15516.67266450654</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nitelva</t>
+          <t>Leira</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rud Nitelva (N8)</t>
+          <t>Leira ved Leirsund (L8)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>Slightly upstream</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5439,41 +6189,41 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>increasing</t>
+          <t>no trend</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.02183878958419649</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>31.19085976211382</v>
+        <v>666.8080196229348</v>
       </c>
       <c r="I21" t="n">
-        <v>55.37928400740564</v>
+        <v>666.8080196229348</v>
       </c>
       <c r="J21" t="n">
-        <v>4.550476830733774</v>
+        <v>666.8080196229348</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jeksla</t>
+          <t>Nitelva</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jeksla ved Haugli, J14</t>
+          <t>Rud Nitelva (N8)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>Downstream</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -5487,37 +6237,37 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8795727890074994</v>
+        <v>0.6780801094706033</v>
       </c>
       <c r="H22" t="n">
-        <v>0.05127000273065783</v>
+        <v>-0.801876395855551</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5797451592095588</v>
+        <v>4.544817532317254</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4899978759244442</v>
+        <v>-6.262280431226346</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jeksla</t>
+          <t>Nitelva</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jeksla ved Haugli, J14</t>
+          <t>Rud Nitelva (N8)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>Downstream</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5531,37 +6281,37 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.9671423309063722</v>
+        <v>0.05775818863725046</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.001387679920261534</v>
+        <v>-0.2079202265961669</v>
       </c>
       <c r="I23" t="n">
-        <v>0.04154665131223973</v>
+        <v>0.01299309778703766</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.05886731056122541</v>
+        <v>-0.4864098227719608</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jeksla</t>
+          <t>Nitelva</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jeksla ved Haugli, J14</t>
+          <t>Rud Nitelva (N8)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>Downstream</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5571,41 +6321,41 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>no trend</t>
+          <t>decreasing</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.6494456692174662</v>
+        <v>0.0130971254873018</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.822632665609356</v>
+        <v>-97.31040128260565</v>
       </c>
       <c r="I24" t="n">
-        <v>27.27245643023724</v>
+        <v>-28.55560601376133</v>
       </c>
       <c r="J24" t="n">
-        <v>-46.03579103678887</v>
+        <v>-153.0466569291263</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jeksla</t>
+          <t>Nitelva</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jeksla ved Haugli, J14</t>
+          <t>Rud Nitelva (N8)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>Downstream</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5619,37 +6369,37 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.03182312738649018</v>
+        <v>0.02183878958419649</v>
       </c>
       <c r="H25" t="n">
-        <v>3.139010042116635</v>
+        <v>31.19085976211382</v>
       </c>
       <c r="I25" t="n">
-        <v>8.3911076468244</v>
+        <v>55.37928400740564</v>
       </c>
       <c r="J25" t="n">
-        <v>1.112764105800906</v>
+        <v>4.550476830733774</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sagelva</t>
+          <t>Jeksla</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sagelva ved Skjetten bro (F3)</t>
+          <t>Jeksla ved Haugli, J14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>Downstream. Small part of regine</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5663,37 +6413,37 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.2783473662511158</v>
+        <v>0.8795727890074994</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3277097710482768</v>
+        <v>0.05127000273065783</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9588469161565655</v>
+        <v>0.5797451592095588</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3595724311563117</v>
+        <v>-0.4899978759244442</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sagelva</t>
+          <t>Jeksla</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sagelva ved Skjetten bro (F3)</t>
+          <t>Jeksla ved Haugli, J14</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>Downstream. Small part of regine</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5703,41 +6453,41 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>increasing</t>
+          <t>no trend</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.02712095825238414</v>
+        <v>0.9671423309063722</v>
       </c>
       <c r="H27" t="n">
-        <v>0.04229539519932368</v>
+        <v>-0.001387679920261534</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09165931053246608</v>
+        <v>0.04154665131223973</v>
       </c>
       <c r="J27" t="n">
-        <v>0.005500908742017459</v>
+        <v>-0.05886731056122541</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sagelva</t>
+          <t>Jeksla</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sagelva ved Skjetten bro (F3)</t>
+          <t>Jeksla ved Haugli, J14</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>Downstream. Small part of regine</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5751,37 +6501,37 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.1961811327385727</v>
+        <v>0.6494456692174662</v>
       </c>
       <c r="H28" t="n">
-        <v>12.96397719477762</v>
+        <v>-2.822632665609356</v>
       </c>
       <c r="I28" t="n">
-        <v>31.31841550383708</v>
+        <v>27.27245643023724</v>
       </c>
       <c r="J28" t="n">
-        <v>-9.630482150512398</v>
+        <v>-46.03579103678887</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sagelva</t>
+          <t>Jeksla</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-30593</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sagelva ved Skjetten bro (F3)</t>
+          <t>Jeksla ved Haugli, J14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Downstream</t>
+          <t>Downstream. Small part of regine</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5795,32 +6545,32 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.002588571976172904</v>
+        <v>0.03182312738649018</v>
       </c>
       <c r="H29" t="n">
-        <v>10.50126200689703</v>
+        <v>3.139010042116635</v>
       </c>
       <c r="I29" t="n">
-        <v>15.54248909451099</v>
+        <v>8.3911076468244</v>
       </c>
       <c r="J29" t="n">
-        <v>3.362789908373056</v>
+        <v>1.112764105800906</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Åa</t>
+          <t>Sagelva</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fossåa ved Sylta (ÅA1)</t>
+          <t>Sagelva ved Skjetten bro (F3)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5839,32 +6589,32 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.5361867719001741</v>
+        <v>0.2783473662511158</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.575836106992045</v>
+        <v>0.3277097710482768</v>
       </c>
       <c r="I30" t="n">
-        <v>21.92485861361903</v>
+        <v>0.9588469161565655</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.1844947619631</v>
+        <v>-0.3595724311563117</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Åa</t>
+          <t>Sagelva</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fossåa ved Sylta (ÅA1)</t>
+          <t>Sagelva ved Skjetten bro (F3)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5879,36 +6629,36 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>no trend</t>
+          <t>increasing</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.5361867719001741</v>
+        <v>0.02712095825238414</v>
       </c>
       <c r="H31" t="n">
-        <v>0.323168857646343</v>
+        <v>0.04229539519932368</v>
       </c>
       <c r="I31" t="n">
-        <v>1.55368975202154</v>
+        <v>0.09165931053246608</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.242008439627743</v>
+        <v>0.005500908742017459</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Åa</t>
+          <t>Sagelva</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fossåa ved Sylta (ÅA1)</t>
+          <t>Sagelva ved Skjetten bro (F3)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5927,32 +6677,32 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.5361867719001741</v>
+        <v>0.1961811327385727</v>
       </c>
       <c r="H32" t="n">
-        <v>389.935244278312</v>
+        <v>12.96397719477762</v>
       </c>
       <c r="I32" t="n">
-        <v>1532.917694873291</v>
+        <v>31.31841550383708</v>
       </c>
       <c r="J32" t="n">
-        <v>-467.3714371825862</v>
+        <v>-9.630482150512398</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Åa</t>
+          <t>Sagelva</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-46599</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fossåa ved Sylta (ÅA1)</t>
+          <t>Sagelva ved Skjetten bro (F3)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5967,41 +6717,41 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>no trend</t>
+          <t>increasing</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0.002588571976172904</v>
       </c>
       <c r="H33" t="n">
-        <v>-13.56832926126446</v>
+        <v>10.50126200689703</v>
       </c>
       <c r="I33" t="n">
-        <v>227.0484350302892</v>
+        <v>15.54248909451099</v>
       </c>
       <c r="J33" t="n">
-        <v>-186.538572334455</v>
+        <v>3.362789908373056</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gansåa</t>
+          <t>Åa</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-60929</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gansåa nedstrøms Dalen RA (BD)</t>
+          <t>Fossåa ved Sylta (ÅA1)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>Downstream</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6015,37 +6765,37 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.9015386266571279</v>
+        <v>0.5361867719001741</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.05601698800040882</v>
+        <v>-3.575836106992045</v>
       </c>
       <c r="I34" t="n">
-        <v>4.160121751449203</v>
+        <v>21.92485861361903</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.208198688647951</v>
+        <v>-17.1844947619631</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Gansåa</t>
+          <t>Åa</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-60929</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gansåa nedstrøms Dalen RA (BD)</t>
+          <t>Fossåa ved Sylta (ÅA1)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>Downstream</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6059,37 +6809,37 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.2655103889538737</v>
+        <v>0.5361867719001741</v>
       </c>
       <c r="H35" t="n">
-        <v>0.04368852423093159</v>
+        <v>0.323168857646343</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2304256015589452</v>
+        <v>1.55368975202154</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1442351100687917</v>
+        <v>-1.242008439627743</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gansåa</t>
+          <t>Åa</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-60929</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gansåa nedstrøms Dalen RA (BD)</t>
+          <t>Fossåa ved Sylta (ÅA1)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>Downstream</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6106,34 +6856,34 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="H36" t="n">
-        <v>14.34707384285408</v>
+        <v>389.935244278312</v>
       </c>
       <c r="I36" t="n">
-        <v>87.55136360349167</v>
+        <v>1532.917694873291</v>
       </c>
       <c r="J36" t="n">
-        <v>-79.39285653432115</v>
+        <v>-467.3714371825862</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gansåa</t>
+          <t>Åa</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-60929</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gansåa nedstrøms Dalen RA (BD)</t>
+          <t>Fossåa ved Sylta (ÅA1)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Downstream. Small part of regine</t>
+          <t>Downstream</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6147,37 +6897,37 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.7105230229164894</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>8.133044202599189</v>
+        <v>-13.56832926126446</v>
       </c>
       <c r="I37" t="n">
-        <v>57.53697936745633</v>
+        <v>227.0484350302892</v>
       </c>
       <c r="J37" t="n">
-        <v>-33.96071005019476</v>
+        <v>-186.538572334455</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sagelva</t>
+          <t>Gansåa</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-60933</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fjellhammarelva (F10)</t>
+          <t>Gansåa nedstrøms Dalen RA (BD)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Slightly upstream</t>
+          <t>Downstream. Small part of regine</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6191,37 +6941,37 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.6693340144640527</v>
+        <v>0.9015386266571279</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5281429905704358</v>
+        <v>-0.05601698800040882</v>
       </c>
       <c r="I38" t="n">
-        <v>1.740134882367078</v>
+        <v>4.160121751449203</v>
       </c>
       <c r="J38" t="n">
-        <v>-2.405590012836732</v>
+        <v>-2.208198688647951</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sagelva</t>
+          <t>Gansåa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-60933</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fjellhammarelva (F10)</t>
+          <t>Gansåa nedstrøms Dalen RA (BD)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Slightly upstream</t>
+          <t>Downstream. Small part of regine</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -6235,59 +6985,235 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.6693340144640527</v>
+        <v>0.2655103889538737</v>
       </c>
       <c r="H39" t="n">
-        <v>0.02916914647222391</v>
+        <v>0.04368852423093159</v>
       </c>
       <c r="I39" t="n">
-        <v>0.246610406161959</v>
+        <v>0.2304256015589452</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.0943439280170939</v>
+        <v>-0.1442351100687917</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Gansåa</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>002-60933</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Gansåa nedstrøms Dalen RA (BD)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Downstream. Small part of regine</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SS_tonn</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>no trend</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.5361867719001741</v>
+      </c>
+      <c r="H40" t="n">
+        <v>14.34707384285408</v>
+      </c>
+      <c r="I40" t="n">
+        <v>87.55136360349167</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-79.39285653432115</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gansåa</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>002-60933</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Gansåa nedstrøms Dalen RA (BD)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Downstream. Small part of regine</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>TOC_tonn</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>no trend</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0.7105230229164894</v>
+      </c>
+      <c r="H41" t="n">
+        <v>8.133044202599189</v>
+      </c>
+      <c r="I41" t="n">
+        <v>57.53697936745633</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-33.96071005019476</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Sagelva</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>002-63540</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Fjellhammarelva (F10)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Slightly upstream</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TOTN_tonn</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>no trend</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0.6693340144640527</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.5281429905704358</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.740134882367078</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-2.405590012836732</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sagelva</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva (F10)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Slightly upstream</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>TOTP_tonn</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>no trend</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0.6693340144640527</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.02916914647222391</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.246610406161959</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-0.0943439280170939</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sagelva</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva (F10)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Slightly upstream</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>SS_tonn</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>no trend</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="G44" t="n">
         <v>0.5829505577618919</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H44" t="n">
         <v>7.828092881049773</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I44" t="n">
         <v>55.79478544822852</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J44" t="n">
         <v>-63.79420127294421</v>
       </c>
     </row>
